--- a/analysis/Statistics - Completion Time Analysis/table 4 linear mixed model time to completions.xlsx
+++ b/analysis/Statistics - Completion Time Analysis/table 4 linear mixed model time to completions.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\misc\GitHub\FuzzDojo\analysis\paper tables and figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SW\Desktop\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" tabRatio="500"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="23263" windowHeight="12463" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Statistics" sheetId="16" r:id="rId1"/>
@@ -174,7 +174,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -244,7 +244,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -626,21 +626,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N47"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="8.7265625" style="1"/>
-    <col min="6" max="6" width="11.08984375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="1"/>
-    <col min="9" max="9" width="15.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.7265625" style="1"/>
-    <col min="13" max="13" width="11.54296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="1"/>
+    <col min="1" max="5" width="8.69140625" style="1"/>
+    <col min="6" max="6" width="11.07421875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="16.15234375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.69140625" style="1"/>
+    <col min="9" max="9" width="15.23046875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.69140625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.69140625" style="1"/>
+    <col min="13" max="14" width="11.53515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -684,7 +683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -728,7 +727,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -772,7 +771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -816,7 +815,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -860,7 +859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -904,7 +903,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -948,7 +947,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -989,7 +988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1033,7 +1032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -1077,7 +1076,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -1121,7 +1120,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -1165,7 +1164,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1209,7 +1208,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
@@ -1253,7 +1252,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
@@ -1297,7 +1296,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -1341,7 +1340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1385,7 +1384,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
@@ -1473,7 +1472,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
@@ -1517,7 +1516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1561,7 +1560,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>2</v>
       </c>
@@ -1605,7 +1604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>2</v>
       </c>
@@ -1649,7 +1648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -1693,7 +1692,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -1737,7 +1736,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -1781,7 +1780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>12</v>
       </c>
@@ -1914,7 +1913,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>2</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>12</v>
       </c>
@@ -1999,7 +1998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>12</v>
       </c>
@@ -2043,7 +2042,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -2087,35 +2086,35 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="11"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
     </row>
   </sheetData>
   <sortState ref="A2:N33">
